--- a/CPRD Raw Analysis/Results/Overall/overall_combined_summary_costs_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/Overall/overall_combined_summary_costs_SOURCE.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -426,154 +426,74 @@
         <v>23106</v>
       </c>
       <c r="C2">
-        <v>757.6900000000001</v>
+        <v>1113.42</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>12916.41</v>
+        <v>19104.33</v>
       </c>
       <c r="F2">
-        <v>767.53</v>
+        <v>1141.63</v>
       </c>
       <c r="G2">
-        <v>535.3</v>
+        <v>782.63</v>
       </c>
       <c r="H2">
-        <v>233.51</v>
+        <v>339.93</v>
       </c>
       <c r="I2">
-        <v>1025.09</v>
+        <v>1508.08</v>
       </c>
       <c r="J2">
-        <v>5.05</v>
+        <v>7.51</v>
       </c>
       <c r="K2">
-        <v>747.79</v>
+        <v>1098.7</v>
       </c>
       <c r="L2">
-        <v>767.59</v>
+        <v>1128.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B3">
-        <v>23106</v>
+        <v>22478</v>
       </c>
       <c r="C3">
-        <v>728.8099999999999</v>
+        <v>1144.26</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="E3">
-        <v>12424</v>
+        <v>19104.33</v>
       </c>
       <c r="F3">
-        <v>747.33</v>
+        <v>1142.25</v>
       </c>
       <c r="G3">
-        <v>514.52</v>
+        <v>810.5599999999999</v>
       </c>
       <c r="H3">
-        <v>222</v>
+        <v>368.36</v>
       </c>
       <c r="I3">
-        <v>989.01</v>
+        <v>1539.36</v>
       </c>
       <c r="J3">
-        <v>4.92</v>
+        <v>7.62</v>
       </c>
       <c r="K3">
-        <v>719.17</v>
+        <v>1129.32</v>
       </c>
       <c r="L3">
-        <v>738.4400000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>22466</v>
-      </c>
-      <c r="C4">
-        <v>779.08</v>
-      </c>
-      <c r="D4">
-        <v>1.9</v>
-      </c>
-      <c r="E4">
-        <v>12916.41</v>
-      </c>
-      <c r="F4">
-        <v>767.7</v>
-      </c>
-      <c r="G4">
-        <v>557.47</v>
-      </c>
-      <c r="H4">
-        <v>254.42</v>
-      </c>
-      <c r="I4">
-        <v>1044.88</v>
-      </c>
-      <c r="J4">
-        <v>5.12</v>
-      </c>
-      <c r="K4">
-        <v>769.04</v>
-      </c>
-      <c r="L4">
-        <v>789.12</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>22466</v>
-      </c>
-      <c r="C5">
-        <v>749.5700000000001</v>
-      </c>
-      <c r="D5">
-        <v>0.95</v>
-      </c>
-      <c r="E5">
-        <v>12424</v>
-      </c>
-      <c r="F5">
-        <v>747.5700000000001</v>
-      </c>
-      <c r="G5">
-        <v>530.16</v>
-      </c>
-      <c r="H5">
-        <v>236.98</v>
-      </c>
-      <c r="I5">
-        <v>1004</v>
-      </c>
-      <c r="J5">
-        <v>4.99</v>
-      </c>
-      <c r="K5">
-        <v>739.79</v>
-      </c>
-      <c r="L5">
-        <v>759.34</v>
+        <v>1159.19</v>
       </c>
     </row>
   </sheetData>
